--- a/data/results_curve_fits_wind_hydrogen.xlsx
+++ b/data/results_curve_fits_wind_hydrogen.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terlouw_t\Documents\Projects\TRANSIENCE\P2_steel_db\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\terlouw_t\Documents\Projects\TRANSIENCE\Steel_CBAM\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93F0D6DC-EC6A-4381-A799-A48178878A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DFB9FA0-163B-470A-93C0-08B3FB1955E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,37 +56,37 @@
     <t>ratio_wind_curtailed_on</t>
   </si>
   <si>
-    <t>ecoinvent_310_reference</t>
-  </si>
-  <si>
-    <t>ecoinvent_image_SSP2-RCP26_2030_base</t>
-  </si>
-  <si>
-    <t>ecoinvent_image_SSP2-RCP26_2035_base</t>
-  </si>
-  <si>
-    <t>ecoinvent_image_SSP2-RCP26_2040_base</t>
-  </si>
-  <si>
-    <t>ecoinvent_image_SSP2-RCP26_2045_base</t>
-  </si>
-  <si>
-    <t>ecoinvent_image_SSP2-RCP26_2050_base</t>
-  </si>
-  <si>
-    <t>ecoinvent_remind_SSP2-PkBudg1150_2030_base</t>
-  </si>
-  <si>
-    <t>ecoinvent_remind_SSP2-PkBudg1150_2035_base</t>
-  </si>
-  <si>
-    <t>ecoinvent_remind_SSP2-PkBudg1150_2040_base</t>
-  </si>
-  <si>
-    <t>ecoinvent_remind_SSP2-PkBudg1150_2045_base</t>
-  </si>
-  <si>
-    <t>ecoinvent_remind_SSP2-PkBudg1150_2050_base</t>
+    <t>ecoinvent_remind_SSP2-PkBudg1000_2030_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_remind_SSP2-PkBudg1000_2035_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_remind_SSP2-PkBudg1000_2040_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_remind_SSP2-PkBudg1000_2045_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_remind_SSP2-PkBudg1000_2050_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_image_SSP2-L_2030_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_image_SSP2-L_2035_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_image_SSP2-L_2040_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_image_SSP2-L_2045_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_image_SSP2-L_2050_base</t>
+  </si>
+  <si>
+    <t>ecoinvent_312_reference</t>
   </si>
 </sst>
 </file>
@@ -542,7 +542,7 @@
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C2">
         <v>-10.83993427535933</v>
@@ -557,7 +557,7 @@
     <row r="3" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6"/>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>-10.802913316171139</v>
@@ -572,7 +572,7 @@
     <row r="4" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="6"/>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C4">
         <v>-10.79289441185826</v>
@@ -587,7 +587,7 @@
     <row r="5" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="6"/>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C5">
         <v>-10.784806576055271</v>
@@ -602,7 +602,7 @@
     <row r="6" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="6"/>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3">
         <f>C5</f>
@@ -620,7 +620,7 @@
     <row r="7" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="6"/>
       <c r="B7" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3">
         <f>C5</f>
@@ -638,7 +638,7 @@
     <row r="8" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="6"/>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C8" s="3">
         <f>C3</f>
@@ -656,7 +656,7 @@
     <row r="9" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="6"/>
       <c r="B9" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3">
         <f t="shared" ref="C9:E12" si="3">C4</f>
@@ -674,7 +674,7 @@
     <row r="10" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="6"/>
       <c r="B10" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" s="3">
         <f t="shared" si="3"/>
@@ -692,7 +692,7 @@
     <row r="11" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="6"/>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3">
         <f t="shared" si="3"/>
@@ -710,7 +710,7 @@
     <row r="12" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="7"/>
       <c r="B12" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C12" s="3">
         <f t="shared" si="3"/>
@@ -730,7 +730,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C13">
         <v>-4.7000336802668299</v>
@@ -745,7 +745,7 @@
     <row r="14" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4"/>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>-4.5812692513554234</v>
@@ -760,7 +760,7 @@
     <row r="15" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4"/>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>-4.368192835547152</v>
@@ -775,7 +775,7 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4"/>
       <c r="B16" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>-3.9515281926096582</v>
@@ -790,7 +790,7 @@
     <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4"/>
       <c r="B17" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C17" s="3">
         <f>C16</f>
@@ -808,7 +808,7 @@
     <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="4"/>
       <c r="B18" s="2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C18" s="3">
         <f>C16</f>
@@ -826,7 +826,7 @@
     <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="4"/>
       <c r="B19" s="2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C19" s="3">
         <f>C14</f>
@@ -844,7 +844,7 @@
     <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4"/>
       <c r="B20" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C20" s="3">
         <f t="shared" ref="C20:E23" si="7">C15</f>
@@ -862,7 +862,7 @@
     <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4"/>
       <c r="B21" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C21" s="3">
         <f t="shared" si="7"/>
@@ -880,7 +880,7 @@
     <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4"/>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C22" s="3">
         <f t="shared" si="7"/>
@@ -898,7 +898,7 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4"/>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C23" s="3">
         <f t="shared" si="7"/>
